--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_23_R3.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_23_R3.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>B. DUNSTON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,40 +565,40 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8983</v>
+        <v>3.8543</v>
       </c>
       <c r="E2" t="n">
-        <v>6.541</v>
+        <v>0.4087</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6427</v>
+        <v>3.4456</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1562</v>
+        <v>2.1102</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2822</v>
+        <v>0.3903</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4384</v>
+        <v>1.7199</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7934</v>
+        <v>0.2985</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6659</v>
+        <v>0.1512</v>
       </c>
       <c r="L2" t="n">
-        <v>1.1275</v>
+        <v>0.1472</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6372</v>
+        <v>1.8118</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9481000000000001</v>
+        <v>0.2391</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6891</v>
+        <v>1.5727</v>
       </c>
       <c r="P2" t="n">
         <v>0.9278</v>
@@ -610,28 +610,28 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7421</v>
+        <v>0.7055</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6033</v>
+        <v>0.1103</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1388</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0722</v>
+        <v>0.1107</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0722</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. DUNSTON</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0081</v>
+        <v>2.8738</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4953</v>
+        <v>4.4493</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5128</v>
+        <v>-1.5755</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1102</v>
+        <v>0.1562</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3903</v>
+        <v>-0.2822</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7199</v>
+        <v>0.4384</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2985</v>
+        <v>1.7934</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1512</v>
+        <v>0.6659</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1472</v>
+        <v>1.1275</v>
       </c>
       <c r="M3" t="n">
-        <v>1.8118</v>
+        <v>-1.6372</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2391</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5727</v>
+        <v>-0.6891</v>
       </c>
       <c r="P3" t="n">
         <v>0.9278</v>
@@ -688,22 +688,22 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8593</v>
+        <v>0.7176</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1968</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6625</v>
+        <v>0.206</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1107</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1107</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0981</v>
+        <v>2.5271</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.5509</v>
+        <v>-0.458</v>
       </c>
       <c r="F4" t="n">
-        <v>2.649</v>
+        <v>2.9851</v>
       </c>
       <c r="G4" t="n">
         <v>2.2812</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.093</v>
+        <v>0.3361</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.963</v>
+        <v>0.13</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.13</v>
+        <v>0.206</v>
       </c>
       <c r="V4" t="n">
         <v>0.1418</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4401</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5867</v>
+        <v>3.1332</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.0268</v>
+        <v>-2.6235</v>
       </c>
       <c r="G5" t="n">
         <v>1.5609</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0912</v>
+        <v>-0.1415</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8883</v>
+        <v>-0.3418</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.203</v>
+        <v>0.2003</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6778999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-0.6963</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1422</v>
+        <v>-2.1108</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2465</v>
+        <v>1.4145</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6343</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2025</v>
+        <v>0.402</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0553</v>
+        <v>0.0868</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1472</v>
+        <v>0.3152</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2677</v>
+        <v>-1.1724</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1129</v>
+        <v>-0.5108</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8452</v>
+        <v>-0.6616</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7457</v>
+        <v>-2.3154</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9794</v>
+        <v>0.0035</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7662</v>
+        <v>-2.3188</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4487</v>
+        <v>-0.9425</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0504</v>
+        <v>0.9515</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4991</v>
+        <v>-1.894</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.297</v>
+        <v>-1.3729</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0299</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7328</v>
+        <v>-0.4248</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.246</v>
+        <v>-0.2693</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6642</v>
+        <v>-0.6405</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9102</v>
+        <v>0.3712</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2525</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BROOKS</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2954</v>
+        <v>-1.2425</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.3381</v>
+        <v>-1.6844</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0427</v>
+        <v>0.4419</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2593</v>
+        <v>-1.7457</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0073</v>
+        <v>-0.9794</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.252</v>
+        <v>-0.7662</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.3163</v>
+        <v>-1.4487</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5615</v>
+        <v>0.0504</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.8778</v>
+        <v>-1.4991</v>
       </c>
       <c r="M8" t="n">
-        <v>0.057</v>
+        <v>-0.297</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5688</v>
+        <v>-1.0299</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6258</v>
+        <v>0.7328</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5696</v>
+        <v>0.2713</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1379</v>
+        <v>-0.2357</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4317</v>
+        <v>0.507</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7142</v>
+        <v>-1.5209</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.1052</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1804</v>
+        <v>-1.4157</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9023</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0233</v>
+        <v>0.17</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8057</v>
+        <v>-0.3771</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7824</v>
+        <v>0.5472</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7886</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>A. BROOKS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.264</v>
+        <v>-1.9697</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1319</v>
+        <v>-3.3067</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1321</v>
+        <v>1.337</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3154</v>
+        <v>-2.2593</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0035</v>
+        <v>-0.0073</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3188</v>
+        <v>-2.252</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9425</v>
+        <v>-2.3163</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9515</v>
+        <v>0.5615</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.894</v>
+        <v>-2.8778</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3729</v>
+        <v>0.057</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.5688</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4248</v>
+        <v>0.6258</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.361</v>
+        <v>0.8953</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2617</v>
+        <v>0.1693</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0993</v>
+        <v>0.726</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2525</v>
+        <v>-0.1418</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8197</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0904</v>
+        <v>-4.006</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7357</v>
+        <v>-1.6178</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3546</v>
+        <v>-2.3883</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7021</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4784</v>
+        <v>-0.3941</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5895</v>
+        <v>-0.4716</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1111</v>
+        <v>0.0775</v>
       </c>
       <c r="V11" t="n">
         <v>-1.214</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.963000000000001</v>
+        <v>-0.8430000000000004</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.922499999999998</v>
+        <v>-1.802500000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9595999999999987</v>
+        <v>0.9595000000000002</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4506</v>
@@ -1363,10 +1363,10 @@
         <v>2.107800000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2868</v>
+        <v>0.2868000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2377000000000002</v>
+        <v>0.2377000000000005</v>
       </c>
       <c r="L12" t="n">
         <v>0.04900000000000015</v>
@@ -1390,13 +1390,13 @@
         <v>8.118499999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5726</v>
+        <v>2.6929</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.1791</v>
+        <v>-1.0587</v>
       </c>
       <c r="U12" t="n">
-        <v>3.7516</v>
+        <v>3.7517</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2451</v>
@@ -1405,7 +1405,7 @@
         <v>5.9282</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.173299999999999</v>
+        <v>-7.173300000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.4763</v>
+        <v>5.574</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7702</v>
+        <v>5.4163</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.1576</v>
       </c>
       <c r="G13" t="n">
         <v>3.2263</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8763</v>
+        <v>0.9739</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2284</v>
+        <v>-0.1254</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6478</v>
+        <v>1.0994</v>
       </c>
       <c r="V13" t="n">
         <v>0.6778999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>E. OKOBO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6283</v>
+        <v>1.3984</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3905</v>
+        <v>0.2486</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7622</v>
+        <v>1.1498</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9159</v>
+        <v>-0.0237</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2568</v>
+        <v>0.3745</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6591</v>
+        <v>-0.3982</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7298</v>
+        <v>-0.2347</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1275</v>
+        <v>-0.1576</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.0771</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1861</v>
+        <v>0.211</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1294</v>
+        <v>0.5321</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0568</v>
+        <v>-0.3211</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>0.637</v>
+        <v>-0.0934</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2284</v>
+        <v>-0.6405</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4086</v>
+        <v>0.5472</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2525</v>
+        <v>0.8197</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8919</v>
+        <v>1.3558</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4597</v>
+        <v>1.1181</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4658</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0061</v>
+        <v>0.5702</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1297</v>
+        <v>-0.2377</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7971</v>
+        <v>1.0806</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9268</v>
+        <v>-1.3183</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1275</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8401999999999999</v>
+        <v>1.2639</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7127</v>
+        <v>-1.7836</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2572</v>
+        <v>0.282</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0431</v>
+        <v>-0.1833</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.214</v>
+        <v>0.4653</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>0.195</v>
+        <v>-0.34</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5702</v>
+        <v>-1.0767</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3752</v>
+        <v>0.7367</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3943</v>
+        <v>0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3943</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4481</v>
+        <v>0.7855</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.754</v>
+        <v>-0.2821</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2021</v>
+        <v>1.0676</v>
       </c>
       <c r="G16" t="n">
         <v>2.7444</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3532</v>
+        <v>-0.0158</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0455</v>
+        <v>-0.5737</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6923</v>
+        <v>0.5579</v>
       </c>
       <c r="V16" t="n">
         <v>1.0722</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. OKOBO</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2868</v>
+        <v>0.6499</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2232</v>
+        <v>0.2299</v>
       </c>
       <c r="F17" t="n">
-        <v>0.51</v>
+        <v>0.4201</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0237</v>
+        <v>-0.1297</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3745</v>
+        <v>0.7971</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3982</v>
+        <v>-0.9268</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2347</v>
+        <v>0.1275</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1576</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0771</v>
+        <v>-0.7127</v>
       </c>
       <c r="M17" t="n">
-        <v>0.211</v>
+        <v>-0.2572</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5321</v>
+        <v>-0.0431</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3211</v>
+        <v>-0.214</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.205</v>
+        <v>0.3853</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1123</v>
+        <v>0.3343</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0927</v>
+        <v>0.051</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8197</v>
+        <v>0.3943</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3558</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5361</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2631</v>
+        <v>0.1958</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1598</v>
+        <v>0.8007</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1033</v>
+        <v>-0.605</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2377</v>
+        <v>-0.9159</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0806</v>
+        <v>-0.2568</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3183</v>
+        <v>-0.6591</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.7298</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2639</v>
+        <v>-0.1275</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.7836</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>0.282</v>
+        <v>-0.1861</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1833</v>
+        <v>-0.1294</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4653</v>
+        <v>-0.0568</v>
       </c>
       <c r="P18" t="n">
         <v>1.1598</v>
@@ -1858,22 +1858,22 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7212</v>
+        <v>0.2045</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.7844</v>
+        <v>-0.3613</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0633</v>
+        <v>0.5658</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5361</v>
+        <v>-0.2525</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1444</v>
+        <v>1.8919</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6083</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7729</v>
+        <v>-0.407</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.67</v>
+        <v>-0.3161</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.103</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0.07140000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1665</v>
+        <v>0.1994</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6642</v>
+        <v>-0.3104</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4977</v>
+        <v>0.5098</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6778999999999999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1273</v>
+        <v>-0.9656</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2</v>
+        <v>-2.7898</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0727</v>
+        <v>1.8241</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3682</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5065</v>
+        <v>-0.3449</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2197</v>
+        <v>-0.8094</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2869</v>
+        <v>0.4646</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2525</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.59</v>
+        <v>-1.0903</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.039</v>
+        <v>-1.921</v>
       </c>
       <c r="F21" t="n">
-        <v>0.449</v>
+        <v>0.8307</v>
       </c>
       <c r="G21" t="n">
         <v>1.0611</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.883</v>
+        <v>-0.3833</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6642</v>
+        <v>-0.5463</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2188</v>
+        <v>0.163</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5828</v>
+        <v>-2.9367</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.004</v>
+        <v>-2.3578</v>
       </c>
       <c r="F22" t="n">
         <v>-0.5788</v>
@@ -2170,10 +2170,10 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5544</v>
+        <v>0.2005</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7117</v>
+        <v>0.3578</v>
       </c>
       <c r="U22" t="n">
         <v>-0.1573</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.963099999999999</v>
+        <v>4.322100000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4234999999999998</v>
+        <v>-0.4234000000000007</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3865</v>
+        <v>4.7454</v>
       </c>
       <c r="G23" t="n">
-        <v>3.4506</v>
+        <v>3.450600000000001</v>
       </c>
       <c r="H23" t="n">
         <v>5.5585</v>
@@ -2221,7 +2221,7 @@
         <v>-2.1077</v>
       </c>
       <c r="J23" t="n">
-        <v>3.737299999999999</v>
+        <v>3.7373</v>
       </c>
       <c r="K23" t="n">
         <v>5.7961</v>
@@ -2236,7 +2236,7 @@
         <v>-0.2377999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.04900000000000004</v>
+        <v>-0.04899999999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-1.1597</v>
@@ -2245,16 +2245,16 @@
         <v>-8.118600000000001</v>
       </c>
       <c r="R23" t="n">
-        <v>6.9588</v>
+        <v>6.958799999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5727</v>
+        <v>0.7862</v>
       </c>
       <c r="T23" t="n">
         <v>-3.7516</v>
       </c>
       <c r="U23" t="n">
-        <v>2.1788</v>
+        <v>4.5381</v>
       </c>
       <c r="V23" t="n">
         <v>1.2451</v>
